--- a/sharedata/excel/D-掉落表(DropData).xlsx
+++ b/sharedata/excel/D-掉落表(DropData).xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\策划文档\配置表\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ThroneOfAshes_Client\sharedata\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="78">
   <si>
     <t>掉落类型表</t>
   </si>
@@ -80,19 +80,22 @@
     <t>权重掉落</t>
   </si>
   <si>
-    <t>根据各配置项权重进行随机抽取；具体抽取次数由掉落组配置决定。</t>
+    <t>按权重抽取draws_times次；num为每次获得数量，repeat控制是否放回。</t>
   </si>
   <si>
     <t>概率掉落</t>
   </si>
   <si>
-    <t>掉落组内每个配置项分别进行独立概率判定，可同时获得多个奖励，也可能全部未命中。</t>
+    <t>每次调用对各物品独立判定一次；weight为0至1的概率，可能全部未命中；不读取draws_times与repeat。</t>
   </si>
   <si>
     <t>玩家自选</t>
   </si>
   <si>
-    <t>根据各配置数量字段玩家可自选多个。</t>
+    <t>选择draws_times个；每项获得num个物品，repeat控制能否重复选择。</t>
+  </si>
+  <si>
+    <t>每项奖励数量</t>
   </si>
   <si>
     <t>权重：A/(A+B+C)</t>
@@ -101,6 +104,9 @@
     <t>不放回抽取代表掉落组物品不会重复</t>
   </si>
   <si>
+    <t>组内一致</t>
+  </si>
+  <si>
     <t>概率：A*100%</t>
   </si>
   <si>
@@ -125,7 +131,7 @@
     <t>权重/概率</t>
   </si>
   <si>
-    <t>抽取次数</t>
+    <t>抽取/自选次数</t>
   </si>
   <si>
     <t>是否放回</t>
@@ -168,6 +174,99 @@
   </si>
   <si>
     <t>ref(ItemData)</t>
+  </si>
+  <si>
+    <t>临时普通宝箱奖励_1</t>
+  </si>
+  <si>
+    <t>临时普通宝箱奖励</t>
+  </si>
+  <si>
+    <t>金币</t>
+  </si>
+  <si>
+    <t>临时普通宝箱奖励_2</t>
+  </si>
+  <si>
+    <t>木材</t>
+  </si>
+  <si>
+    <t>临时普通宝箱奖励_3</t>
+  </si>
+  <si>
+    <t>临时小兵_1</t>
+  </si>
+  <si>
+    <t>临时精良宝箱奖励_1</t>
+  </si>
+  <si>
+    <t>临时精良宝箱奖励</t>
+  </si>
+  <si>
+    <t>临时精良宝箱奖励_2</t>
+  </si>
+  <si>
+    <t>装备强化石</t>
+  </si>
+  <si>
+    <t>临时精良宝箱奖励_3</t>
+  </si>
+  <si>
+    <t>临时史诗宝箱奖励_1</t>
+  </si>
+  <si>
+    <t>临时史诗宝箱奖励</t>
+  </si>
+  <si>
+    <t>临时史诗宝箱奖励_2</t>
+  </si>
+  <si>
+    <t>临时守卫_武器</t>
+  </si>
+  <si>
+    <t>临时史诗宝箱奖励_3</t>
+  </si>
+  <si>
+    <t>临时英雄_1</t>
+  </si>
+  <si>
+    <t>临时传说宝箱奖励_1</t>
+  </si>
+  <si>
+    <t>临时传说宝箱奖励</t>
+  </si>
+  <si>
+    <t>神器经验石</t>
+  </si>
+  <si>
+    <t>临时传说宝箱奖励_2</t>
+  </si>
+  <si>
+    <t>临时统御徽记</t>
+  </si>
+  <si>
+    <t>临时传说宝箱奖励_3</t>
+  </si>
+  <si>
+    <t>临时英雄_2</t>
+  </si>
+  <si>
+    <t>临时神迹宝箱奖励_1</t>
+  </si>
+  <si>
+    <t>临时神迹宝箱奖励</t>
+  </si>
+  <si>
+    <t>钻石</t>
+  </si>
+  <si>
+    <t>临时神迹宝箱奖励_2</t>
+  </si>
+  <si>
+    <t>临时守望旗帜</t>
+  </si>
+  <si>
+    <t>临时神迹宝箱奖励_3</t>
   </si>
 </sst>
 </file>
@@ -198,6 +297,13 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -357,13 +463,6 @@
       <sz val="12"/>
       <name val="宋体"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-      <b/>
-      <color rgb="FFFF0000"/>
     </font>
   </fonts>
   <fills count="34">
@@ -692,160 +791,160 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" applyFill="0">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -853,23 +952,20 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="53">
@@ -1348,10 +1444,10 @@
   <dimension ref="A1:D9"/>
   <sheetFormatPr defaultColWidth="10.125" defaultRowHeight="16.5" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="15" style="1" customWidth="1"/>
-    <col min="2" max="2" width="8.875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="10.875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="65" style="5" customWidth="1"/>
+    <col min="1" max="1" width="15.125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="5.625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="12.125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="99.875" style="7" customWidth="1"/>
     <col min="5" max="6" width="13.75" style="1" customWidth="1"/>
     <col min="7" max="7" width="7" style="1" customWidth="1"/>
     <col min="8" max="8" width="7.625" style="1" customWidth="1"/>
@@ -1359,25 +1455,25 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:4">
-      <c r="A1" s="3"/>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="5"/>
+      <c r="A1" s="4"/>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="7"/>
     </row>
     <row r="2" s="1" customFormat="1" spans="1:4">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="5"/>
+      <c r="A2" s="4"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="7"/>
     </row>
     <row r="3" s="2" customFormat="1" spans="1:4">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="4" t="s">
+      <c r="B3" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="5" t="s">
         <v>2</v>
       </c>
       <c r="D3" s="2" t="s">
@@ -1385,13 +1481,13 @@
       </c>
     </row>
     <row r="4" s="2" customFormat="1" spans="1:4">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="5" t="s">
         <v>6</v>
       </c>
       <c r="D4" s="2" t="s">
@@ -1399,13 +1495,13 @@
       </c>
     </row>
     <row r="5" s="2" customFormat="1" spans="1:4">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="5" t="s">
         <v>10</v>
       </c>
       <c r="D5" s="2" t="s">
@@ -1413,54 +1509,48 @@
       </c>
     </row>
     <row r="6" s="2" customFormat="1" spans="1:4">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="4"/>
+      <c r="C6" s="5"/>
       <c r="D6" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="42" customHeight="1">
+    <row r="7" spans="1:4">
       <c r="B7" s="1">
         <v>1</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>按权重抽取draws_times次；num为每次获得数量，repeat控制是否放回。</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="62" customHeight="1">
+      <c r="D7" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
       <c r="B8" s="1">
         <v>2</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>每次调用对各物品独立判定一次；weight为0至1的概率，可能全部未命中；不读取draws_times与repeat。</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="42" customHeight="1">
+      <c r="D8" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
       <c r="B9" s="1">
         <v>3</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>选择draws_times个；每项获得num个物品，repeat控制能否重复选择。</t>
-        </is>
+      <c r="D9" s="7" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -1473,150 +1563,139 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:K21"/>
-  <sheetFormatPr defaultColWidth="10.125" defaultRowHeight="16.5" outlineLevelRow="5"/>
+  <sheetFormatPr defaultColWidth="10.125" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="15" style="1" customWidth="1"/>
-    <col min="2" max="2" width="8.875" style="1" customWidth="1"/>
-    <col min="3" max="4" width="10.875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="12.875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="10.125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="8.125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="19.375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="9.625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="17.125" style="1" customWidth="1"/>
     <col min="6" max="6" width="19.375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="13.75" style="1" customWidth="1"/>
-    <col min="8" max="8" width="20.125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="16.25" style="1" customWidth="1"/>
-    <col min="10" max="10" width="17.125" style="1" customWidth="1"/>
-    <col min="11" max="16383" width="10.125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="13.875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="12.875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="17.625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="13.75" style="1" customWidth="1"/>
+    <col min="11" max="11" width="33.75" style="1" customWidth="1"/>
+    <col min="12" max="21" width="10.125" style="1" customWidth="1"/>
+    <col min="22" max="16384" width="10.125" style="3"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:11">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>同组适用的类型、次数、放回参数保持一致。</t>
-        </is>
-      </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
+      <c r="A1" s="4"/>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
       <c r="E1" s="1"/>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>每项奖励数量</t>
-        </is>
+      <c r="H1" s="3" t="s">
+        <v>20</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" spans="1:11">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
+      <c r="A2" s="4"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
       <c r="E2" s="1"/>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>组内一致</t>
-        </is>
+      <c r="F2" s="3" t="s">
+        <v>23</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>组内一致</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>组内一致</t>
-        </is>
+        <v>24</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="3" s="2" customFormat="1" spans="1:11">
-      <c r="A3" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="4" t="s">
+      <c r="A3" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>24</v>
+      <c r="D3" s="5" t="s">
+        <v>26</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>抽取/自选次数</t>
-        </is>
+        <v>31</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>32</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" s="2" customFormat="1" spans="1:11">
-      <c r="A4" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B4" s="4" t="s">
+      <c r="A4" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>33</v>
+      <c r="D4" s="5" t="s">
+        <v>35</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5" s="2" customFormat="1" spans="1:11">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E5" s="2" t="s">
@@ -1632,489 +1711,489 @@
         <v>9</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6" s="2" customFormat="1" spans="1:11">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="5"/>
       <c r="E6" s="2"/>
       <c r="F6" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="7" ht="49.5" customHeight="1">
-      <c r="B7" t="n" s="7">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="B7" s="6">
         <v>610101</v>
       </c>
-      <c r="C7" t="str" s="8">
-        <v>临时普通宝箱奖励_1</v>
-      </c>
-      <c r="D7" t="n" s="7">
+      <c r="C7" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="D7" s="6">
         <v>6101</v>
       </c>
-      <c r="E7" t="str" s="8">
-        <v>临时普通宝箱奖励</v>
-      </c>
-      <c r="F7" t="str" s="7">
-        <v>权重掉落</v>
-      </c>
-      <c r="G7" t="str" s="7">
-        <v>金币</v>
-      </c>
-      <c r="H7" t="n" s="7">
+      <c r="E7" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="H7" s="6">
         <v>1000</v>
       </c>
-      <c r="I7" t="n" s="7">
+      <c r="I7" s="6">
         <v>60</v>
       </c>
-      <c r="J7" t="n" s="7">
-        <v>1</v>
-      </c>
-      <c r="K7" t="b" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" ht="49.5" customHeight="1">
-      <c r="B8" t="n" s="7">
+      <c r="J7" s="6">
+        <v>1</v>
+      </c>
+      <c r="K7" s="6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="B8" s="6">
         <v>610102</v>
       </c>
-      <c r="C8" t="str" s="8">
-        <v>临时普通宝箱奖励_2</v>
-      </c>
-      <c r="D8" t="n" s="7">
+      <c r="C8" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="D8" s="6">
         <v>6101</v>
       </c>
-      <c r="E8" s="7"/>
-      <c r="F8" t="str" s="7">
-        <v>权重掉落</v>
-      </c>
-      <c r="G8" t="str" s="7">
-        <v>木材</v>
-      </c>
-      <c r="H8" t="n" s="7">
+      <c r="E8" s="6"/>
+      <c r="F8" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="H8" s="6">
         <v>100</v>
       </c>
-      <c r="I8" t="n" s="7">
+      <c r="I8" s="6">
         <v>30</v>
       </c>
-      <c r="J8" t="n" s="7">
-        <v>1</v>
-      </c>
-      <c r="K8" t="b" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" ht="49.5" customHeight="1">
-      <c r="B9" t="n" s="7">
+      <c r="J8" s="6">
+        <v>1</v>
+      </c>
+      <c r="K8" s="6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="B9" s="6">
         <v>610103</v>
       </c>
-      <c r="C9" t="str" s="8">
-        <v>临时普通宝箱奖励_3</v>
-      </c>
-      <c r="D9" t="n" s="7">
+      <c r="C9" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="D9" s="6">
         <v>6101</v>
       </c>
-      <c r="E9" s="7"/>
-      <c r="F9" t="str" s="7">
-        <v>权重掉落</v>
-      </c>
-      <c r="G9" t="str" s="7">
-        <v>临时小兵_1</v>
-      </c>
-      <c r="H9" t="n" s="7">
+      <c r="E9" s="6"/>
+      <c r="F9" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="H9" s="6">
         <v>5</v>
       </c>
-      <c r="I9" t="n" s="7">
+      <c r="I9" s="6">
         <v>10</v>
       </c>
-      <c r="J9" t="n" s="7">
-        <v>1</v>
-      </c>
-      <c r="K9" t="b" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" ht="49.5" customHeight="1">
-      <c r="B10" t="n" s="7">
+      <c r="J9" s="6">
+        <v>1</v>
+      </c>
+      <c r="K9" s="6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="B10" s="6">
         <v>610201</v>
       </c>
-      <c r="C10" t="str" s="8">
-        <v>临时精良宝箱奖励_1</v>
-      </c>
-      <c r="D10" t="n" s="7">
+      <c r="C10" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="D10" s="6">
         <v>6102</v>
       </c>
-      <c r="E10" t="str" s="8">
-        <v>临时精良宝箱奖励</v>
-      </c>
-      <c r="F10" t="str" s="7">
-        <v>权重掉落</v>
-      </c>
-      <c r="G10" t="str" s="7">
-        <v>金币</v>
-      </c>
-      <c r="H10" t="n" s="7">
+      <c r="E10" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="H10" s="6">
         <v>2000</v>
       </c>
-      <c r="I10" t="n" s="7">
+      <c r="I10" s="6">
         <v>50</v>
       </c>
-      <c r="J10" t="n" s="7">
+      <c r="J10" s="6">
         <v>2</v>
       </c>
-      <c r="K10" t="b" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" ht="49.5" customHeight="1">
-      <c r="B11" t="n" s="7">
+      <c r="K10" s="6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="B11" s="6">
         <v>610202</v>
       </c>
-      <c r="C11" t="str" s="8">
-        <v>临时精良宝箱奖励_2</v>
-      </c>
-      <c r="D11" t="n" s="7">
+      <c r="C11" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="D11" s="6">
         <v>6102</v>
       </c>
-      <c r="E11" s="7"/>
-      <c r="F11" t="str" s="7">
-        <v>权重掉落</v>
-      </c>
-      <c r="G11" t="str" s="7">
-        <v>装备强化石</v>
-      </c>
-      <c r="H11" t="n" s="7">
+      <c r="E11" s="6"/>
+      <c r="F11" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="H11" s="6">
         <v>5</v>
       </c>
-      <c r="I11" t="n" s="7">
+      <c r="I11" s="6">
         <v>30</v>
       </c>
-      <c r="J11" t="n" s="7">
+      <c r="J11" s="6">
         <v>2</v>
       </c>
-      <c r="K11" t="b" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" ht="49.5" customHeight="1">
-      <c r="B12" t="n" s="7">
+      <c r="K11" s="6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="B12" s="6">
         <v>610203</v>
       </c>
-      <c r="C12" t="str" s="8">
-        <v>临时精良宝箱奖励_3</v>
-      </c>
-      <c r="D12" t="n" s="7">
+      <c r="C12" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D12" s="6">
         <v>6102</v>
       </c>
-      <c r="E12" s="7"/>
-      <c r="F12" t="str" s="7">
-        <v>权重掉落</v>
-      </c>
-      <c r="G12" t="str" s="7">
-        <v>临时小兵_1</v>
-      </c>
-      <c r="H12" t="n" s="7">
+      <c r="E12" s="6"/>
+      <c r="F12" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="H12" s="6">
         <v>10</v>
       </c>
-      <c r="I12" t="n" s="7">
+      <c r="I12" s="6">
         <v>20</v>
       </c>
-      <c r="J12" t="n" s="7">
+      <c r="J12" s="6">
         <v>2</v>
       </c>
-      <c r="K12" t="b" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" ht="49.5" customHeight="1">
-      <c r="B13" t="n" s="7">
+      <c r="K12" s="6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="B13" s="6">
         <v>610301</v>
       </c>
-      <c r="C13" t="str" s="8">
-        <v>临时史诗宝箱奖励_1</v>
-      </c>
-      <c r="D13" t="n" s="7">
+      <c r="C13" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="D13" s="6">
         <v>6103</v>
       </c>
-      <c r="E13" t="str" s="8">
-        <v>临时史诗宝箱奖励</v>
-      </c>
-      <c r="F13" t="str" s="7">
-        <v>权重掉落</v>
-      </c>
-      <c r="G13" t="str" s="7">
-        <v>装备强化石</v>
-      </c>
-      <c r="H13" t="n" s="7">
+      <c r="E13" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="H13" s="6">
         <v>10</v>
       </c>
-      <c r="I13" t="n" s="7">
+      <c r="I13" s="6">
         <v>50</v>
       </c>
-      <c r="J13" t="n" s="7">
+      <c r="J13" s="6">
         <v>3</v>
       </c>
-      <c r="K13" t="b" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" ht="49.5" customHeight="1">
-      <c r="B14" t="n" s="7">
+      <c r="K13" s="6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="B14" s="6">
         <v>610302</v>
       </c>
-      <c r="C14" t="str" s="8">
-        <v>临时史诗宝箱奖励_2</v>
-      </c>
-      <c r="D14" t="n" s="7">
+      <c r="C14" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D14" s="6">
         <v>6103</v>
       </c>
-      <c r="E14" s="7"/>
-      <c r="F14" t="str" s="7">
-        <v>权重掉落</v>
-      </c>
-      <c r="G14" t="str" s="8">
-        <v>临时守卫_武器</v>
-      </c>
-      <c r="H14" t="n" s="7">
-        <v>1</v>
-      </c>
-      <c r="I14" t="n" s="7">
+      <c r="E14" s="6"/>
+      <c r="F14" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="H14" s="6">
+        <v>1</v>
+      </c>
+      <c r="I14" s="6">
         <v>30</v>
       </c>
-      <c r="J14" t="n" s="7">
+      <c r="J14" s="6">
         <v>3</v>
       </c>
-      <c r="K14" t="b" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" ht="49.5" customHeight="1">
-      <c r="B15" t="n" s="7">
+      <c r="K14" s="6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="B15" s="6">
         <v>610303</v>
       </c>
-      <c r="C15" t="str" s="8">
-        <v>临时史诗宝箱奖励_3</v>
-      </c>
-      <c r="D15" t="n" s="7">
+      <c r="C15" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="D15" s="6">
         <v>6103</v>
       </c>
-      <c r="E15" s="7"/>
-      <c r="F15" t="str" s="7">
-        <v>权重掉落</v>
-      </c>
-      <c r="G15" t="str" s="7">
-        <v>临时英雄_1</v>
-      </c>
-      <c r="H15" t="n" s="7">
-        <v>1</v>
-      </c>
-      <c r="I15" t="n" s="7">
+      <c r="E15" s="6"/>
+      <c r="F15" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G15" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="H15" s="6">
+        <v>1</v>
+      </c>
+      <c r="I15" s="6">
         <v>20</v>
       </c>
-      <c r="J15" t="n" s="7">
+      <c r="J15" s="6">
         <v>3</v>
       </c>
-      <c r="K15" t="b" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" ht="49.5" customHeight="1">
-      <c r="B16" t="n" s="7">
+      <c r="K15" s="6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="B16" s="6">
         <v>610401</v>
       </c>
-      <c r="C16" t="str" s="8">
-        <v>临时传说宝箱奖励_1</v>
-      </c>
-      <c r="D16" t="n" s="7">
+      <c r="C16" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="D16" s="6">
         <v>6104</v>
       </c>
-      <c r="E16" t="str" s="8">
-        <v>临时传说宝箱奖励</v>
-      </c>
-      <c r="F16" t="str" s="7">
-        <v>权重掉落</v>
-      </c>
-      <c r="G16" t="str" s="7">
-        <v>神器经验石</v>
-      </c>
-      <c r="H16" t="n" s="7">
+      <c r="E16" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="H16" s="6">
         <v>10</v>
       </c>
-      <c r="I16" t="n" s="7">
+      <c r="I16" s="6">
         <v>50</v>
       </c>
-      <c r="J16" t="n" s="7">
+      <c r="J16" s="6">
         <v>4</v>
       </c>
-      <c r="K16" t="b" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" ht="49.5" customHeight="1">
-      <c r="B17" t="n" s="7">
+      <c r="K16" s="6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="2:11">
+      <c r="B17" s="6">
         <v>610402</v>
       </c>
-      <c r="C17" t="str" s="8">
-        <v>临时传说宝箱奖励_2</v>
-      </c>
-      <c r="D17" t="n" s="7">
+      <c r="C17" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="D17" s="6">
         <v>6104</v>
       </c>
-      <c r="E17" s="7"/>
-      <c r="F17" t="str" s="7">
-        <v>权重掉落</v>
-      </c>
-      <c r="G17" t="str" s="8">
-        <v>临时统御徽记</v>
-      </c>
-      <c r="H17" t="n" s="7">
-        <v>1</v>
-      </c>
-      <c r="I17" t="n" s="7">
+      <c r="E17" s="6"/>
+      <c r="F17" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G17" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="H17" s="6">
+        <v>1</v>
+      </c>
+      <c r="I17" s="6">
         <v>30</v>
       </c>
-      <c r="J17" t="n" s="7">
+      <c r="J17" s="6">
         <v>4</v>
       </c>
-      <c r="K17" t="b" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" ht="49.5" customHeight="1">
-      <c r="B18" t="n" s="7">
+      <c r="K17" s="6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="2:11">
+      <c r="B18" s="6">
         <v>610403</v>
       </c>
-      <c r="C18" t="str" s="8">
-        <v>临时传说宝箱奖励_3</v>
-      </c>
-      <c r="D18" t="n" s="7">
+      <c r="C18" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="D18" s="6">
         <v>6104</v>
       </c>
-      <c r="E18" s="7"/>
-      <c r="F18" t="str" s="7">
-        <v>权重掉落</v>
-      </c>
-      <c r="G18" t="str" s="7">
-        <v>临时英雄_2</v>
-      </c>
-      <c r="H18" t="n" s="7">
-        <v>1</v>
-      </c>
-      <c r="I18" t="n" s="7">
+      <c r="E18" s="6"/>
+      <c r="F18" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="H18" s="6">
+        <v>1</v>
+      </c>
+      <c r="I18" s="6">
         <v>20</v>
       </c>
-      <c r="J18" t="n" s="7">
+      <c r="J18" s="6">
         <v>4</v>
       </c>
-      <c r="K18" t="b" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" ht="49.5" customHeight="1">
-      <c r="B19" t="n" s="7">
+      <c r="K18" s="6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="2:11">
+      <c r="B19" s="6">
         <v>610501</v>
       </c>
-      <c r="C19" t="str" s="8">
-        <v>临时神迹宝箱奖励_1</v>
-      </c>
-      <c r="D19" t="n" s="7">
+      <c r="C19" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="D19" s="6">
         <v>6105</v>
       </c>
-      <c r="E19" t="str" s="8">
-        <v>临时神迹宝箱奖励</v>
-      </c>
-      <c r="F19" t="str" s="7">
-        <v>权重掉落</v>
-      </c>
-      <c r="G19" t="str" s="7">
-        <v>钻石</v>
-      </c>
-      <c r="H19" t="n" s="7">
+      <c r="E19" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G19" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="H19" s="6">
         <v>100</v>
       </c>
-      <c r="I19" t="n" s="7">
+      <c r="I19" s="6">
         <v>50</v>
       </c>
-      <c r="J19" t="n" s="7">
+      <c r="J19" s="6">
         <v>5</v>
       </c>
-      <c r="K19" t="b" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" ht="49.5" customHeight="1">
-      <c r="B20" t="n" s="7">
+      <c r="K19" s="6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="2:11">
+      <c r="B20" s="6">
         <v>610502</v>
       </c>
-      <c r="C20" t="str" s="8">
-        <v>临时神迹宝箱奖励_2</v>
-      </c>
-      <c r="D20" t="n" s="7">
+      <c r="C20" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="D20" s="6">
         <v>6105</v>
       </c>
-      <c r="E20" s="7"/>
-      <c r="F20" t="str" s="7">
-        <v>权重掉落</v>
-      </c>
-      <c r="G20" t="str" s="8">
-        <v>临时守望旗帜</v>
-      </c>
-      <c r="H20" t="n" s="7">
-        <v>1</v>
-      </c>
-      <c r="I20" t="n" s="7">
+      <c r="E20" s="6"/>
+      <c r="F20" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G20" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="H20" s="6">
+        <v>1</v>
+      </c>
+      <c r="I20" s="6">
         <v>30</v>
       </c>
-      <c r="J20" t="n" s="7">
+      <c r="J20" s="6">
         <v>5</v>
       </c>
-      <c r="K20" t="b" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" ht="49.5" customHeight="1">
-      <c r="B21" t="n" s="7">
+      <c r="K20" s="6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="2:11">
+      <c r="B21" s="6">
         <v>610503</v>
       </c>
-      <c r="C21" t="str" s="8">
-        <v>临时神迹宝箱奖励_3</v>
-      </c>
-      <c r="D21" t="n" s="7">
+      <c r="C21" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="D21" s="6">
         <v>6105</v>
       </c>
-      <c r="E21" s="7"/>
-      <c r="F21" t="str" s="7">
-        <v>权重掉落</v>
-      </c>
-      <c r="G21" t="str" s="7">
-        <v>临时英雄_1</v>
-      </c>
-      <c r="H21" t="n" s="7">
-        <v>1</v>
-      </c>
-      <c r="I21" t="n" s="7">
+      <c r="E21" s="6"/>
+      <c r="F21" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G21" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="H21" s="6">
+        <v>1</v>
+      </c>
+      <c r="I21" s="6">
         <v>20</v>
       </c>
-      <c r="J21" t="n" s="7">
+      <c r="J21" s="6">
         <v>5</v>
       </c>
-      <c r="K21" t="b" s="7">
+      <c r="K21" s="6" t="b">
         <v>1</v>
       </c>
     </row>
